--- a/data/trending_integrated_20261030_13.xlsx
+++ b/data/trending_integrated_20261030_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25700</v>
+        <v>25500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+185.56%</t>
+          <t>'+183.33%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>782</v>
+        <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G2" t="n">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>672160682115</v>
+        <v>699193997040</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -622,20 +622,20 @@
         <v>-169000</v>
       </c>
       <c r="S2" t="n">
-        <v>-89000</v>
+        <v>-90000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주 급등 기대감 속 목표가 25000원 제시. 26년 IPO 대장주 언급과 당기순이익 250억 확인.</t>
+          <t>신규 상장주로서의 급등락 반복 및 목표가 제시. IPO 대장주 언급과 함께 투기적인 기대감이 높으나, 주가 조작 및 하락 패턴에 대한 우려도 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장', 'IPO', '당기순이익']</t>
+          <t>['신규 상장', 'IPO', '급등락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7500</v>
+        <v>7460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.19%</t>
+          <t>'+19.55%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F3" t="n">
         <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>29032444535</v>
+        <v>29566730815</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19380</v>
+        <v>19360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.40%</t>
+          <t>'+16.28%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>112026256465</v>
+        <v>114518646055</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -806,20 +806,20 @@
         <v>94000</v>
       </c>
       <c r="S4" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11월 양자관련법 시행 최대 수혜주로 부각. 정부 양자 보안 의무화 및 바이낸스, 빗썸 해킹 사태 관련 최대 수혜 기대.</t>
+          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주로 부각. 기술력과 시장 지배력을 바탕으로 한 최대 수혜주로서의 기대감이 높음. 관련 뉴스 및 정책 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', '수혜주', '해킹']</t>
+          <t>['양자 보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2785</v>
+        <v>2760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.67%</t>
+          <t>'+12.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>12513143873</v>
+        <v>12586929218</v>
       </c>
       <c r="P5" t="n">
         <v>3170</v>
@@ -895,7 +895,7 @@
         <v>880</v>
       </c>
       <c r="R5" t="n">
-        <v>-14000</v>
+        <v>-23000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8650</v>
+        <v>8600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.34%</t>
+          <t>'+11.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>8332383145</v>
+        <v>8379723055</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -987,7 +987,7 @@
         <v>7060</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>-70000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12060</v>
+        <v>12010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.68%</t>
+          <t>'+7.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F7" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G7" t="n">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>51168899525</v>
+        <v>52033259855</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15850</v>
+        <v>15870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.81%</t>
+          <t>'+5.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="H8" t="n">
         <v>7.15</v>
@@ -1162,7 +1162,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>47006666460</v>
+        <v>48133799970</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1171,10 +1171,10 @@
         <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>109000</v>
+        <v>101000</v>
       </c>
       <c r="S8" t="n">
-        <v>168000</v>
+        <v>189000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29200</v>
+        <v>29350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H9" t="n">
         <v>4.69</v>
@@ -1254,7 +1254,7 @@
         <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>115983603125</v>
+        <v>116689103275</v>
       </c>
       <c r="P9" t="n">
         <v>50600</v>
@@ -1266,7 +1266,7 @@
         <v>-45000</v>
       </c>
       <c r="S9" t="n">
-        <v>95000</v>
+        <v>188000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50300</v>
+        <v>50900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+3.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H10" t="n">
         <v>23.82</v>
@@ -1346,7 +1346,7 @@
         <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>58383010350</v>
+        <v>58898374250</v>
       </c>
       <c r="P10" t="n">
         <v>97900</v>
@@ -1355,10 +1355,10 @@
         <v>30950</v>
       </c>
       <c r="R10" t="n">
-        <v>-37000</v>
+        <v>2000</v>
       </c>
       <c r="S10" t="n">
-        <v>55000</v>
+        <v>69000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
         <v>66</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>44858856935</v>
+        <v>46144898680</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1447,10 +1447,10 @@
         <v>15320</v>
       </c>
       <c r="R11" t="n">
-        <v>345000</v>
+        <v>700000</v>
       </c>
       <c r="S11" t="n">
-        <v>35000</v>
+        <v>-15000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61600</v>
+        <v>3990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>301</v>
+        <v>199</v>
       </c>
       <c r="H12" t="n">
-        <v>41.76</v>
+        <v>1.43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>62800</v>
+        <v>4040</v>
       </c>
       <c r="K12" t="n">
-        <v>62300</v>
+        <v>3925</v>
       </c>
       <c r="L12" t="n">
-        <v>62800</v>
+        <v>4265</v>
       </c>
       <c r="M12" t="n">
-        <v>60700</v>
+        <v>3880</v>
       </c>
       <c r="N12" t="n">
-        <v>41.55</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>78958763850</v>
+        <v>78237437830</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>117000</v>
+        <v>-37000</v>
       </c>
       <c r="S12" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['상승', '기대감', '외국인매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3960</v>
+        <v>61850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.98%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>194</v>
+        <v>313</v>
       </c>
       <c r="H13" t="n">
-        <v>1.43</v>
+        <v>41.76</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4040</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>3925</v>
+        <v>62300</v>
       </c>
       <c r="L13" t="n">
-        <v>4265</v>
+        <v>62800</v>
       </c>
       <c r="M13" t="n">
-        <v>3880</v>
+        <v>60700</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>77988854610</v>
+        <v>80843999850</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>55000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-81000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['상승', '기대감', '외국인매수']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7290</v>
+        <v>7310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-1.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H14" t="n">
         <v>25.3</v>
@@ -1714,7 +1714,7 @@
         <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>9046787200</v>
+        <v>9236853020</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1723,10 +1723,10 @@
         <v>7010</v>
       </c>
       <c r="R14" t="n">
-        <v>95000</v>
+        <v>76000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-7000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1759,92 +1759,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6430</v>
+        <v>222000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-4.31%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>529</v>
       </c>
       <c r="G15" t="n">
-        <v>83</v>
+        <v>1353</v>
       </c>
       <c r="H15" t="n">
-        <v>0.85</v>
+        <v>46.17</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6640</v>
+        <v>232000</v>
       </c>
       <c r="K15" t="n">
-        <v>7210</v>
+        <v>223500</v>
       </c>
       <c r="L15" t="n">
-        <v>7500</v>
+        <v>229500</v>
       </c>
       <c r="M15" t="n">
-        <v>6340</v>
+        <v>216500</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>31304307340</v>
+        <v>2440562872000</v>
       </c>
       <c r="P15" t="n">
-        <v>9820</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4000</v>
+        <v>94500</v>
       </c>
       <c r="R15" t="n">
-        <v>-63000</v>
+        <v>664000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-505000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>이재용 상속세 관련 정치적 논쟁과 경영 퇴출 요구. 전반적인 내용이 정치적 비난에 집중되어 있으며, 주가에 대한 구체적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['상속세', '정치', '경영']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54150</v>
+        <v>54200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.50%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F16" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G16" t="n">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H16" t="n">
         <v>22.14</v>
@@ -1898,7 +1898,7 @@
         <v>22.34</v>
       </c>
       <c r="O16" t="n">
-        <v>75481848750</v>
+        <v>76914311300</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1907,23 +1907,23 @@
         <v>53400</v>
       </c>
       <c r="R16" t="n">
-        <v>-136000</v>
+        <v>-238000</v>
       </c>
       <c r="S16" t="n">
-        <v>-41000</v>
+        <v>-81000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 확인. 체코 원전 수주 실패 관련 부정적 언급.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['SMR 수주', '실적 개선', '뉴스케일파워']</t>
+          <t>['SMR', '원자로 수주', '실적']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H17" t="n">
         <v>2.67</v>
@@ -1984,13 +1984,13 @@
         <v>11150</v>
       </c>
       <c r="M17" t="n">
-        <v>8110</v>
+        <v>8070</v>
       </c>
       <c r="N17" t="n">
         <v>2.66</v>
       </c>
       <c r="O17" t="n">
-        <v>28757020200</v>
+        <v>29079817110</v>
       </c>
       <c r="P17" t="n">
         <v>19270</v>
@@ -1999,23 +1999,23 @@
         <v>2135</v>
       </c>
       <c r="R17" t="n">
-        <v>-363000</v>
+        <v>-381000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>-1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>서울반도체 대비 높은 영업이익과 환기 해제 기대감. 제2의 한미반도체 및 초전도체 관련 기술 부각.</t>
+          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['영업이익', '환기', '광반도체']</t>
+          <t>['영업이익', '환기', '광통신']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,123 +2035,123 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11030</v>
+        <v>6310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.08%</t>
+          <t>'-4.97%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>377</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>1159</v>
+        <v>79</v>
       </c>
       <c r="H18" t="n">
-        <v>9.73</v>
+        <v>0.85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>11620</v>
+        <v>6640</v>
       </c>
       <c r="K18" t="n">
-        <v>11300</v>
+        <v>7210</v>
       </c>
       <c r="L18" t="n">
-        <v>11470</v>
+        <v>7500</v>
       </c>
       <c r="M18" t="n">
-        <v>10890</v>
+        <v>6300</v>
       </c>
       <c r="N18" t="n">
-        <v>9.6</v>
+        <v>0.9</v>
       </c>
       <c r="O18" t="n">
-        <v>49863398820</v>
+        <v>31496954260</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>9820</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>4000</v>
       </c>
       <c r="R18" t="n">
-        <v>-213000</v>
+        <v>-63000</v>
       </c>
       <c r="S18" t="n">
-        <v>-60000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>가덕도 공사비 증액 및 재건 사업 기대감. 공매도 금지 조치에 따른 영향 분석.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['가덕도', '공사비', '재건']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>219500</v>
+        <v>11040</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.39%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>389</v>
       </c>
       <c r="F19" t="n">
-        <v>537</v>
+        <v>174</v>
       </c>
       <c r="G19" t="n">
-        <v>1398</v>
+        <v>1196</v>
       </c>
       <c r="H19" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K19" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L19" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M19" t="n">
-        <v>216500</v>
+        <v>10890</v>
       </c>
       <c r="N19" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2373545920000</v>
+        <v>50788048110</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>951000</v>
+        <v>-450000</v>
       </c>
       <c r="S19" t="n">
-        <v>-298000</v>
+        <v>-75000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 논란과 정부 정책 비판으로 인한 주가 하락 우려. 대국민 사기극 언급.</t>
+          <t>원전, 가덕도 공사 증액 및 공매도 금지 조치 관련 긍정적 언급. 공시 기반의 구체적인 호재보다는 정부 정책 및 기대감에 대한 논의가 주를 이룸.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상속세', '정치', '주가하락']</t>
+          <t>['원전', '가덕도', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>172300</v>
+        <v>173300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.31%</t>
+          <t>'-5.76%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>543956891050</v>
+        <v>554030004300</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2275,10 +2275,10 @@
         <v>71000</v>
       </c>
       <c r="R20" t="n">
-        <v>-416000</v>
+        <v>-658000</v>
       </c>
       <c r="S20" t="n">
-        <v>-18000</v>
+        <v>-4000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22050</v>
+        <v>22150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.57%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F21" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G21" t="n">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H21" t="n">
         <v>11.6</v>
@@ -2358,7 +2358,7 @@
         <v>12.23</v>
       </c>
       <c r="O21" t="n">
-        <v>76412364300</v>
+        <v>77401119350</v>
       </c>
       <c r="P21" t="n">
         <v>59300</v>
@@ -2367,14 +2367,14 @@
         <v>21100</v>
       </c>
       <c r="R21" t="n">
-        <v>-580000</v>
+        <v>-650000</v>
       </c>
       <c r="S21" t="n">
-        <v>-192000</v>
+        <v>-235000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 사업 관련 긍정적 뉴스(RE100, 물량 완판)에도 불구하고 급락세 지속.</t>
+          <t>주가 누르기 의혹, 유증 및 실적 턴어라운드에도 불구하고 지속되는 급락에 대한 불만. 긍정적 실적 지표 언급에도 불구하고 주가 하락에 대한 부정적 심리가 강함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 누르기', '태양광', 'RE100']</t>
+          <t>['주가 누르기', '유증', '실적']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1407000</v>
+        <v>1418000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.80%</t>
+          <t>'-7.08%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G22" t="n">
-        <v>1282</v>
+        <v>1269</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>2972336526000</v>
+        <v>3027685455500</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2459,23 +2459,23 @@
         <v>501000</v>
       </c>
       <c r="R22" t="n">
-        <v>-165000</v>
+        <v>-202000</v>
       </c>
       <c r="S22" t="n">
-        <v>-76000</v>
+        <v>-107000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>글로벌 반도체 시장 및 AI 투자 확대 속 SK하이닉스 주가 급락에 대한 불만 토로. 정부 정책 비판.</t>
+          <t>정치적 이슈와 증시 전반의 하락세 속에서 SK하이닉스의 주가 하락에 대한 불만. AI 투자 확대 등 긍정적 재료 언급에도 불구하고 전반적인 시장 상황과 정치적 요인이 부정적 sentiment에 영향.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '주가급락']</t>
+          <t>['AI 투자', '증시 하락', '정치']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13720</v>
+        <v>13790</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.72%</t>
+          <t>'-8.25%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G23" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>43203192930</v>
+        <v>43701533695</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2551,10 +2551,10 @@
         <v>1830</v>
       </c>
       <c r="R23" t="n">
-        <v>-118000</v>
+        <v>-180000</v>
       </c>
       <c r="S23" t="n">
-        <v>-23000</v>
+        <v>-51000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2591,18 +2591,18 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7100</v>
+        <v>7160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.13%</t>
+          <t>'-9.37%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
         <v>40</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>15890461985</v>
+        <v>15995144655</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2643,7 +2643,7 @@
         <v>952</v>
       </c>
       <c r="R24" t="n">
-        <v>1000</v>
+        <v>-28000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2679,70 +2679,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14240</v>
+        <v>116600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-16.24%</t>
+          <t>'-15.63%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="G25" t="n">
-        <v>198</v>
+        <v>452</v>
       </c>
       <c r="H25" t="n">
-        <v>0.66</v>
+        <v>14.2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17000</v>
+        <v>138200</v>
       </c>
       <c r="K25" t="n">
-        <v>14000</v>
+        <v>132600</v>
       </c>
       <c r="L25" t="n">
-        <v>15280</v>
+        <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>12930</v>
+        <v>114300</v>
       </c>
       <c r="N25" t="n">
-        <v>0.65</v>
+        <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>53356026985</v>
+        <v>153692579850</v>
       </c>
       <c r="P25" t="n">
-        <v>28800</v>
+        <v>198000</v>
       </c>
       <c r="Q25" t="n">
-        <v>11550</v>
+        <v>36450</v>
       </c>
       <c r="R25" t="n">
-        <v>-24000</v>
+        <v>-346000</v>
       </c>
       <c r="S25" t="n">
-        <v>-170000</v>
+        <v>-69000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>보호예수 물량 매도와 반도체 섹터 약세 속 하락. 마이크론 퀄테스트 통과 및 ASML 장비 수주 공시 기대.</t>
+          <t>대덕전자가 2시간 만에 13% 하락하며 투자자들의 불안감을 키우고 있습니다. 실적에 대한 기대와 달리 급락하는 이유에 대한 의문이 제기되고 있습니다.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['보호예수', '장비수주', '반도체']</t>
+          <t>['실적', '하락', '기판']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,77 +2764,77 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>114900</v>
+        <v>14320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-16.86%</t>
+          <t>'-15.76%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.26</v>
+        <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>168</v>
+        <v>229</v>
       </c>
       <c r="F26" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="G26" t="n">
-        <v>439</v>
+        <v>208</v>
       </c>
       <c r="H26" t="n">
-        <v>14.2</v>
+        <v>0.66</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>138200</v>
+        <v>17000</v>
       </c>
       <c r="K26" t="n">
-        <v>132600</v>
+        <v>14000</v>
       </c>
       <c r="L26" t="n">
-        <v>132900</v>
+        <v>15280</v>
       </c>
       <c r="M26" t="n">
-        <v>114300</v>
+        <v>12930</v>
       </c>
       <c r="N26" t="n">
-        <v>14.46</v>
+        <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>150009740700</v>
+        <v>55750992645</v>
       </c>
       <c r="P26" t="n">
-        <v>198000</v>
+        <v>28800</v>
       </c>
       <c r="Q26" t="n">
-        <v>36450</v>
+        <v>11550</v>
       </c>
       <c r="R26" t="n">
-        <v>-312000</v>
+        <v>-24000</v>
       </c>
       <c r="S26" t="n">
-        <v>-29000</v>
+        <v>-182000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 급락하는 모습. SK하이닉스 소캠2 물량 확대 뉴스에도 불구하고 투자 심리 위축.</t>
+          <t>보호예수 물량 부담 및 장비 수주 공시 지연에 따른 주가 급락. 해외 기관 및 국내 투자자들의 매도세가 강하며, 주가 하락에 대한 부정적 심리가 지배적.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['실적', '급락', '소캠2']</t>
+          <t>['보호예수', '장비 수주', '매도세']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10710</v>
+        <v>10560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.60%</t>
+          <t>'-29.60%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="F27" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G27" t="n">
-        <v>815</v>
+        <v>831</v>
       </c>
       <c r="H27" t="n">
         <v>3.05</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>127060306250</v>
+        <v>128250613195</v>
       </c>
       <c r="P27" t="n">
         <v>12700</v>
@@ -2922,11 +2922,11 @@
         <v>-41000</v>
       </c>
       <c r="S27" t="n">
-        <v>-216000</v>
+        <v>-259000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>상장 첫날 급락 후 반등 기대. 인텔리빅스와 비교하며 크리에이츠의 높은 영업이익(216억)과 작년 매출(1042억) 강조. 주식수 적음 언급.</t>
+          <t>높은 영업이익과 매출액을 기반으로 한 상승 기대감. 인텔리빅스와 비교하며 알짜배기 기업임을 강조. 주가 상승 모멘텀에 대한 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['공모가', '영업이익', '매출']</t>
+          <t>['영업이익', '매출액', '알짜배기']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2970,13 +2970,13 @@
         <v>1.45</v>
       </c>
       <c r="E28" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -3002,7 +3002,7 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>7474588757</v>
+        <v>7484920577</v>
       </c>
       <c r="P28" t="n">
         <v>5700</v>
@@ -3011,23 +3011,23 @@
         <v>1401</v>
       </c>
       <c r="R28" t="n">
-        <v>73000</v>
+        <v>-30000</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>하한가 기록 후 상폐 가능성 제기. 3자배정 유증 납입 일정 및 투자사 관련 불확실성 존재. 관리종목 및 하한가 반복 우려.</t>
+          <t>납입 관련 불확실성 및 연이은 하한가로 인한 상폐 우려. 투자사 및 대표 관련 언급이 있으나, 실질적인 납입 공시 지연으로 부정적인 sentiment가 극대화됨.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['상폐', '하한가', '유증']</t>
+          <t>['납입', '하한가', '상폐']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_13.xlsx
+++ b/data/trending_integrated_20261030_13.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25500</v>
+        <v>24650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+183.33%</t>
+          <t>'+173.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G2" t="n">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>699193997040</v>
+        <v>727284002165</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -619,14 +619,14 @@
         <v>16450</v>
       </c>
       <c r="R2" t="n">
-        <v>-169000</v>
+        <v>-174000</v>
       </c>
       <c r="S2" t="n">
         <v>-90000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주로서의 급등락 반복 및 목표가 제시. IPO 대장주 언급과 함께 투기적인 기대감이 높으나, 주가 조작 및 하락 패턴에 대한 우려도 공존.</t>
+          <t>신규 상장주에 대한 기대와 우려 혼재. 단기 변동성 속 목표가 제시 및 패턴 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장', 'IPO', '급등락']</t>
+          <t>['신규 상장', 'IPO', '당기순이익']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7460</v>
+        <v>19770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.55%</t>
+          <t>'+18.74%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6240</v>
+        <v>16650</v>
       </c>
       <c r="K3" t="n">
-        <v>6700</v>
+        <v>16830</v>
       </c>
       <c r="L3" t="n">
-        <v>7880</v>
+        <v>19900</v>
       </c>
       <c r="M3" t="n">
-        <v>6330</v>
+        <v>16750</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>29566730815</v>
+        <v>120960714715</v>
       </c>
       <c r="P3" t="n">
-        <v>16620</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>4600</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>9000</v>
+        <v>67000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>지수 급락 속 상한가 기대감. 건설업 활성화와 주포의 움직임 관찰. 유증 성공 여부 주목.</t>
+          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주로 부각. 기술력 및 향후 성장성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상한가', '건설', '주포']</t>
+          <t>['양자 보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19360</v>
+        <v>7290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.28%</t>
+          <t>'+16.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16650</v>
+        <v>6240</v>
       </c>
       <c r="K4" t="n">
-        <v>16830</v>
+        <v>6700</v>
       </c>
       <c r="L4" t="n">
-        <v>19800</v>
+        <v>7880</v>
       </c>
       <c r="M4" t="n">
-        <v>16750</v>
+        <v>6330</v>
       </c>
       <c r="N4" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>114518646055</v>
+        <v>30891286710</v>
       </c>
       <c r="P4" t="n">
-        <v>22450</v>
+        <v>16620</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>4600</v>
       </c>
       <c r="R4" t="n">
-        <v>94000</v>
+        <v>-1000</v>
       </c>
       <c r="S4" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주로 부각. 기술력과 시장 지배력을 바탕으로 한 최대 수혜주로서의 기대감이 높음. 관련 뉴스 및 정책 언급.</t>
+          <t>지수 급락 속 상한가 기대감. 건설업 활성화와 주포의 움직임 관찰. 유증 성공 여부 주목.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자 보안', '해킹', '수혜주']</t>
+          <t>['상한가', '건설', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2760</v>
+        <v>2800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.65%</t>
+          <t>'+14.29%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
         <v>0.79</v>
@@ -886,7 +886,7 @@
         <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>12586929218</v>
+        <v>12634615233</v>
       </c>
       <c r="P5" t="n">
         <v>3170</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8600</v>
+        <v>8560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.69%</t>
+          <t>'+11.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H6" t="n">
         <v>13.29</v>
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>8379723055</v>
+        <v>8476975930</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12010</v>
+        <v>15950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.23%</t>
+          <t>'+6.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>887</v>
+        <v>386</v>
       </c>
       <c r="H7" t="n">
-        <v>15.04</v>
+        <v>7.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11200</v>
+        <v>14980</v>
       </c>
       <c r="K7" t="n">
-        <v>13500</v>
+        <v>14980</v>
       </c>
       <c r="L7" t="n">
-        <v>13710</v>
+        <v>16150</v>
       </c>
       <c r="M7" t="n">
-        <v>11750</v>
+        <v>14610</v>
       </c>
       <c r="N7" t="n">
-        <v>15.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>52033259855</v>
+        <v>50390415620</v>
       </c>
       <c r="P7" t="n">
-        <v>18960</v>
+        <v>49800</v>
       </c>
       <c r="Q7" t="n">
-        <v>5730</v>
+        <v>8180</v>
       </c>
       <c r="R7" t="n">
-        <v>-275000</v>
+        <v>101000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 미국 보험 등재 기대. 공매도 영향 속 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['LED', '기술개발', '시장석권']</t>
+          <t>['FDA 승인', '공매도', '헬스케어']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15870</v>
+        <v>11830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.94%</t>
+          <t>'+5.62%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="G8" t="n">
-        <v>375</v>
+        <v>898</v>
       </c>
       <c r="H8" t="n">
-        <v>7.15</v>
+        <v>15.04</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14980</v>
+        <v>11200</v>
       </c>
       <c r="K8" t="n">
-        <v>14980</v>
+        <v>13500</v>
       </c>
       <c r="L8" t="n">
-        <v>16150</v>
+        <v>13710</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>11750</v>
       </c>
       <c r="N8" t="n">
-        <v>8.050000000000001</v>
+        <v>15.08</v>
       </c>
       <c r="O8" t="n">
-        <v>48133799970</v>
+        <v>53350128245</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>18960</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>5730</v>
       </c>
       <c r="R8" t="n">
-        <v>101000</v>
+        <v>-396000</v>
       </c>
       <c r="S8" t="n">
-        <v>189000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
+          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
+          <t>['LED', '기술개발', '시장석권']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29350</v>
+        <v>29600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.63%</t>
+          <t>'+5.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="H9" t="n">
         <v>4.69</v>
@@ -1254,7 +1254,7 @@
         <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>116689103275</v>
+        <v>119444454700</v>
       </c>
       <c r="P9" t="n">
         <v>50600</v>
@@ -1263,7 +1263,7 @@
         <v>13210</v>
       </c>
       <c r="R9" t="n">
-        <v>-45000</v>
+        <v>-12000</v>
       </c>
       <c r="S9" t="n">
         <v>188000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50900</v>
+        <v>51300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.67%</t>
+          <t>'+4.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.82</v>
       </c>
       <c r="E10" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
         <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H10" t="n">
         <v>23.82</v>
@@ -1346,7 +1346,7 @@
         <v>24.64</v>
       </c>
       <c r="O10" t="n">
-        <v>58898374250</v>
+        <v>61029815700</v>
       </c>
       <c r="P10" t="n">
         <v>97900</v>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표에도 지수 영향으로 인한 하락. TC본더 매출 본격화 및 HBM 시대 재도래 수혜 기대.</t>
+          <t>사상 최대 실적 발표 및 TC본더 매출 본격화 기대. HBM 관련 성장성과 공매도 세력과의 경쟁.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15800</v>
+        <v>15820</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.51%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>46144898680</v>
+        <v>46984693685</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3990</v>
+        <v>4010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
         <v>199</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>78237437830</v>
+        <v>78940054578</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1539,7 +1539,7 @@
         <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-37000</v>
+        <v>78000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61850</v>
+        <v>61900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
         <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H13" t="n">
         <v>41.76</v>
@@ -1622,7 +1622,7 @@
         <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>80843999850</v>
+        <v>84374012000</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7310</v>
+        <v>7305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
         <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="H14" t="n">
         <v>25.3</v>
@@ -1714,7 +1714,7 @@
         <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>9236853020</v>
+        <v>9433758915</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>222000</v>
+        <v>223500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.31%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G15" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="H15" t="n">
         <v>46.17</v>
@@ -1806,7 +1806,7 @@
         <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>2440562872000</v>
+        <v>2539695424750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 정치적 논쟁과 경영 퇴출 요구. 전반적인 내용이 정치적 비난에 집중되어 있으며, 주가에 대한 구체적인 팩트 기반 분석은 부족함.</t>
+          <t>이재용 상속세 관련 논란 속 주가 하락 및 경영 퇴출 주장. 정책 및 시장 전반에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상속세', '정치', '경영']</t>
+          <t>['상속세', '주가 조작', '국장']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54200</v>
+        <v>54400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F16" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G16" t="n">
-        <v>1037</v>
+        <v>1070</v>
       </c>
       <c r="H16" t="n">
         <v>22.14</v>
@@ -1898,7 +1898,7 @@
         <v>22.34</v>
       </c>
       <c r="O16" t="n">
-        <v>76914311300</v>
+        <v>78887167300</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8190</v>
+        <v>11080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-4.65%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E17" t="n">
-        <v>109</v>
+        <v>397</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="G17" t="n">
-        <v>291</v>
+        <v>1236</v>
       </c>
       <c r="H17" t="n">
-        <v>2.67</v>
+        <v>9.73</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8580</v>
+        <v>11620</v>
       </c>
       <c r="K17" t="n">
-        <v>11090</v>
+        <v>11300</v>
       </c>
       <c r="L17" t="n">
-        <v>11150</v>
+        <v>11470</v>
       </c>
       <c r="M17" t="n">
-        <v>8070</v>
+        <v>10890</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>9.6</v>
       </c>
       <c r="O17" t="n">
-        <v>29079817110</v>
+        <v>52394898000</v>
       </c>
       <c r="P17" t="n">
-        <v>19270</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>2135</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-381000</v>
+        <v>-450000</v>
       </c>
       <c r="S17" t="n">
-        <v>-1000</v>
+        <v>-75000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
+          <t>원전, 가덕도 공사비 증액, 공매도 금지 조치 등 정부 정책 관련 긍정적 기대감. 러시아-우크라이나 재건 사업 수혜 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['영업이익', '환기', '광통신']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6310</v>
+        <v>175300</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.97%</t>
+          <t>'-4.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>-0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="H18" t="n">
-        <v>0.85</v>
+        <v>74.87</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6640</v>
+        <v>183900</v>
       </c>
       <c r="K18" t="n">
-        <v>7210</v>
+        <v>176800</v>
       </c>
       <c r="L18" t="n">
-        <v>7500</v>
+        <v>179000</v>
       </c>
       <c r="M18" t="n">
-        <v>6300</v>
+        <v>168100</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9</v>
+        <v>75</v>
       </c>
       <c r="O18" t="n">
-        <v>31496954260</v>
+        <v>580053715550</v>
       </c>
       <c r="P18" t="n">
-        <v>9820</v>
+        <v>243500</v>
       </c>
       <c r="Q18" t="n">
-        <v>4000</v>
+        <v>71000</v>
       </c>
       <c r="R18" t="n">
-        <v>-63000</v>
+        <v>-658000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11040</v>
+        <v>22450</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>389</v>
+        <v>245</v>
       </c>
       <c r="F19" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G19" t="n">
-        <v>1196</v>
+        <v>597</v>
       </c>
       <c r="H19" t="n">
-        <v>9.73</v>
+        <v>11.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>11620</v>
+        <v>23600</v>
       </c>
       <c r="K19" t="n">
-        <v>11300</v>
+        <v>22650</v>
       </c>
       <c r="L19" t="n">
-        <v>11470</v>
+        <v>22700</v>
       </c>
       <c r="M19" t="n">
-        <v>10890</v>
+        <v>21100</v>
       </c>
       <c r="N19" t="n">
-        <v>9.6</v>
+        <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>50788048110</v>
+        <v>79823094125</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>59300</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>21100</v>
       </c>
       <c r="R19" t="n">
-        <v>-450000</v>
+        <v>-650000</v>
       </c>
       <c r="S19" t="n">
-        <v>-75000</v>
+        <v>-235000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전, 가덕도 공사 증액 및 공매도 금지 조치 관련 긍정적 언급. 공시 기반의 구체적인 호재보다는 정부 정책 및 기대감에 대한 논의가 주를 이룸.</t>
+          <t>주가 누르기 의혹, 유증 및 실적 턴어라운드에도 불구하고 지속되는 급락에 대한 불만. 긍정적 실적 지표 언급에도 불구하고 주가 하락에 대한 부정적 심리가 강함.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도']</t>
+          <t>['주가 누르기', '유증', '실적']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,191 +2212,191 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173300</v>
+        <v>8150</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.76%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="H20" t="n">
-        <v>74.87</v>
+        <v>2.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>183900</v>
+        <v>8580</v>
       </c>
       <c r="K20" t="n">
-        <v>176800</v>
+        <v>11090</v>
       </c>
       <c r="L20" t="n">
-        <v>179000</v>
+        <v>11150</v>
       </c>
       <c r="M20" t="n">
-        <v>168100</v>
+        <v>8070</v>
       </c>
       <c r="N20" t="n">
-        <v>75</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>554030004300</v>
+        <v>29320608630</v>
       </c>
       <c r="P20" t="n">
-        <v>243500</v>
+        <v>19270</v>
       </c>
       <c r="Q20" t="n">
-        <v>71000</v>
+        <v>2135</v>
       </c>
       <c r="R20" t="n">
-        <v>-658000</v>
+        <v>-381000</v>
       </c>
       <c r="S20" t="n">
-        <v>-4000</v>
+        <v>-1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['영업이익', '환기', '광통신']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22150</v>
+        <v>6280</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.14%</t>
+          <t>'-5.42%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.63</v>
+        <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>241</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>591</v>
+        <v>81</v>
       </c>
       <c r="H21" t="n">
-        <v>11.6</v>
+        <v>0.85</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>23600</v>
+        <v>6640</v>
       </c>
       <c r="K21" t="n">
-        <v>22650</v>
+        <v>7210</v>
       </c>
       <c r="L21" t="n">
-        <v>22700</v>
+        <v>7500</v>
       </c>
       <c r="M21" t="n">
-        <v>21100</v>
+        <v>6230</v>
       </c>
       <c r="N21" t="n">
-        <v>12.23</v>
+        <v>0.9</v>
       </c>
       <c r="O21" t="n">
-        <v>77401119350</v>
+        <v>31849877720</v>
       </c>
       <c r="P21" t="n">
-        <v>59300</v>
+        <v>9820</v>
       </c>
       <c r="Q21" t="n">
-        <v>21100</v>
+        <v>4000</v>
       </c>
       <c r="R21" t="n">
-        <v>-650000</v>
+        <v>-55000</v>
       </c>
       <c r="S21" t="n">
-        <v>-235000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 누르기 의혹, 유증 및 실적 턴어라운드에도 불구하고 지속되는 급락에 대한 불만. 긍정적 실적 지표 언급에도 불구하고 주가 하락에 대한 부정적 심리가 강함.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 누르기', '유증', '실적']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1418000</v>
+        <v>1431000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.08%</t>
+          <t>'-6.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G22" t="n">
-        <v>1269</v>
+        <v>1296</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3027685455500</v>
+        <v>3143960621000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈와 증시 전반의 하락세 속에서 SK하이닉스의 주가 하락에 대한 불만. AI 투자 확대 등 긍정적 재료 언급에도 불구하고 전반적인 시장 상황과 정치적 요인이 부정적 sentiment에 영향.</t>
+          <t>엔비디아 회복 및 AI 투자 확대 기대감 속 개인 투자자들의 불안감 표출. 정부 정책 및 시장 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['AI 투자', '증시 하락', '정치']</t>
+          <t>['엔비디아', 'AI 투자', '자사주 매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13790</v>
+        <v>13880</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.25%</t>
+          <t>'-7.65%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>65</v>
       </c>
       <c r="G23" t="n">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>43701533695</v>
+        <v>44477490655</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7160</v>
+        <v>7170</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.37%</t>
+          <t>'-9.24%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
         <v>135</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>15995144655</v>
+        <v>16170976745</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116600</v>
+        <v>119300</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-15.63%</t>
+          <t>'-13.68%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F25" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G25" t="n">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>153692579850</v>
+        <v>162372467600</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14320</v>
+        <v>14100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-15.76%</t>
+          <t>'-17.06%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F26" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G26" t="n">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>55750992645</v>
+        <v>60639407995</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2827,14 +2827,14 @@
         <v>11550</v>
       </c>
       <c r="R26" t="n">
-        <v>-24000</v>
+        <v>57000</v>
       </c>
       <c r="S26" t="n">
         <v>-182000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 부담 및 장비 수주 공시 지연에 따른 주가 급락. 해외 기관 및 국내 투자자들의 매도세가 강하며, 주가 하락에 대한 부정적 심리가 지배적.</t>
+          <t>반도체 업황 부진 속 보호예수 물량 및 프로그램 매도 우려. 장비 수주 공시 및 ASML 관련 기대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '장비 수주', '매도세']</t>
+          <t>['보호예수', '장비 수주', '마이크론']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2863,79 +2863,79 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>벡트로보틱스</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10560</v>
+        <v>1805</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-29.60%</t>
+          <t>'-29.90%</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E27" t="n">
+        <v>103</v>
+      </c>
+      <c r="F27" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" t="n">
+        <v>97</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7489575672</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="S27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>483</v>
-      </c>
-      <c r="F27" t="n">
-        <v>208</v>
-      </c>
-      <c r="G27" t="n">
-        <v>831</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L27" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M27" t="n">
-        <v>9790</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>128250613195</v>
-      </c>
-      <c r="P27" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>9790</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-41000</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-259000</v>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>높은 영업이익과 매출액을 기반으로 한 상승 기대감. 인텔리빅스와 비교하며 알짜배기 기업임을 강조. 주가 상승 모멘텀에 대한 긍정적 전망 제시.</t>
+          <t>신규 상장 후 하한가 행진 및 상폐 우려. 납입 이슈와 주가 하락에 대한 불안감.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['영업이익', '매출액', '알짜배기']</t>
+          <t>['상장', '하한가', '납입']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2948,38 +2948,38 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>439270</t>
+          <t>457600</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1805</v>
+        <v>10330</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-29.90%</t>
+          <t>'-31.13%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>97</v>
+        <v>497</v>
       </c>
       <c r="F28" t="n">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="G28" t="n">
-        <v>94</v>
+        <v>843</v>
       </c>
       <c r="H28" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,47 +2987,47 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2575</v>
+        <v>15000</v>
       </c>
       <c r="K28" t="n">
-        <v>1960</v>
+        <v>12000</v>
       </c>
       <c r="L28" t="n">
-        <v>2005</v>
+        <v>12700</v>
       </c>
       <c r="M28" t="n">
-        <v>1805</v>
+        <v>9790</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>7484920577</v>
+        <v>130992610585</v>
       </c>
       <c r="P28" t="n">
-        <v>5700</v>
+        <v>12700</v>
       </c>
       <c r="Q28" t="n">
-        <v>1401</v>
+        <v>9790</v>
       </c>
       <c r="R28" t="n">
-        <v>-30000</v>
+        <v>-41000</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-259000</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>납입 관련 불확실성 및 연이은 하한가로 인한 상폐 우려. 투자사 및 대표 관련 언급이 있으나, 실질적인 납입 공시 지연으로 부정적인 sentiment가 극대화됨.</t>
+          <t>인텔리빅스와의 실적 비교 우위 강조. 상장 초기 급등 기대감 및 주포 역할에 대한 관심.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['납입', '하한가', '상폐']</t>
+          <t>['당기순이익', '실적', '주포']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>439270</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261030_13.xlsx
+++ b/data/trending_integrated_20261030_13.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24650</v>
+        <v>24300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+173.89%</t>
+          <t>'+170.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G2" t="n">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>727284002165</v>
+        <v>757712698890</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주에 대한 기대와 우려 혼재. 단기 변동성 속 목표가 제시 및 패턴 분석.</t>
+          <t>정부 정책 지원 가능성과 AI 관련 성장 기대감을 보이는 한편, 급격한 가격 변동성에 대한 우려도 존재함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장', 'IPO', '당기순이익']</t>
+          <t>['AI', '신규상장', '주가 변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19770</v>
+        <v>19320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.74%</t>
+          <t>'+16.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -702,7 +702,7 @@
         <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>120960714715</v>
+        <v>124838093280</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주로 부각. 기술력 및 향후 성장성에 대한 긍정적 전망.</t>
+          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주로서 단기 급등에 대한 기대감이 높으며, 기술력에 대한 긍정적 평가가 있음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자 보안', '해킹', '수혜주']</t>
+          <t>['양자 보안', '해킹 수혜', '기술력']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7290</v>
+        <v>7180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.83%</t>
+          <t>'+15.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>30891286710</v>
+        <v>31413870875</v>
       </c>
       <c r="P4" t="n">
         <v>16620</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2800</v>
+        <v>2775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.29%</t>
+          <t>'+13.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.16</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>35</v>
@@ -886,7 +886,7 @@
         <v>0.63</v>
       </c>
       <c r="O5" t="n">
-        <v>12634615233</v>
+        <v>12682189998</v>
       </c>
       <c r="P5" t="n">
         <v>3170</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8560</v>
+        <v>8680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.17%</t>
+          <t>'+12.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>8476975930</v>
+        <v>8613549080</v>
       </c>
       <c r="P6" t="n">
         <v>13670</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15950</v>
+        <v>51600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.48%</t>
+          <t>'+5.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="H7" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K7" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L7" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M7" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N7" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O7" t="n">
-        <v>50390415620</v>
+        <v>62192078100</v>
       </c>
       <c r="P7" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q7" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R7" t="n">
-        <v>101000</v>
+        <v>2000</v>
       </c>
       <c r="S7" t="n">
-        <v>189000</v>
+        <v>69000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 미국 보험 등재 기대. 공매도 영향 속 상승 추세 전망.</t>
+          <t>역대 최대 실적 발표에도 불구하고 주가가 지지부진한 상황에 대한 불만과 함께, 공매도 세력과의 공방 속 상승 기대감이 있음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '헬스케어']</t>
+          <t>['실적', '공매도', 'TC본더']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11830</v>
+        <v>29450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.62%</t>
+          <t>'+4.99%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>-0.36</v>
       </c>
       <c r="E8" t="n">
-        <v>312</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>898</v>
+        <v>323</v>
       </c>
       <c r="H8" t="n">
-        <v>15.04</v>
+        <v>4.69</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11200</v>
+        <v>28050</v>
       </c>
       <c r="K8" t="n">
-        <v>13500</v>
+        <v>27850</v>
       </c>
       <c r="L8" t="n">
-        <v>13710</v>
+        <v>30400</v>
       </c>
       <c r="M8" t="n">
-        <v>11750</v>
+        <v>27650</v>
       </c>
       <c r="N8" t="n">
-        <v>15.08</v>
+        <v>5.05</v>
       </c>
       <c r="O8" t="n">
-        <v>53350128245</v>
+        <v>121672983950</v>
       </c>
       <c r="P8" t="n">
-        <v>18960</v>
+        <v>50600</v>
       </c>
       <c r="Q8" t="n">
-        <v>5730</v>
+        <v>13210</v>
       </c>
       <c r="R8" t="n">
-        <v>-396000</v>
+        <v>-12000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>188000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LED', '기술개발', '시장석권']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29600</v>
+        <v>15680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.53%</t>
+          <t>'+4.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>318</v>
+        <v>394</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,143 +1239,143 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L9" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M9" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N9" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>119444454700</v>
+        <v>51620635620</v>
       </c>
       <c r="P9" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-12000</v>
+        <v>101000</v>
       </c>
       <c r="S9" t="n">
-        <v>188000</v>
+        <v>189000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 미국 보험 등재 기대. 공매도 영향 속 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['FDA 승인', '공매도', '헬스케어']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51300</v>
+        <v>11710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.48%</t>
+          <t>'+4.55%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.82</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="G10" t="n">
-        <v>220</v>
+        <v>915</v>
       </c>
       <c r="H10" t="n">
-        <v>23.82</v>
+        <v>15.04</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>49100</v>
+        <v>11200</v>
       </c>
       <c r="K10" t="n">
-        <v>49450</v>
+        <v>13500</v>
       </c>
       <c r="L10" t="n">
-        <v>52000</v>
+        <v>13710</v>
       </c>
       <c r="M10" t="n">
-        <v>48050</v>
+        <v>11620</v>
       </c>
       <c r="N10" t="n">
-        <v>24.64</v>
+        <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>61029815700</v>
+        <v>54564939160</v>
       </c>
       <c r="P10" t="n">
-        <v>97900</v>
+        <v>18960</v>
       </c>
       <c r="Q10" t="n">
-        <v>30950</v>
+        <v>5730</v>
       </c>
       <c r="R10" t="n">
-        <v>2000</v>
+        <v>-396000</v>
       </c>
       <c r="S10" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표 및 TC본더 매출 본격화 기대. HBM 관련 성장성과 공매도 세력과의 경쟁.</t>
+          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', 'HBM']</t>
+          <t>['LED', '기술개발', '시장석권']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>46984693685</v>
+        <v>48120663680</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4010</v>
+        <v>4055</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>78940054578</v>
+        <v>79966009615</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61900</v>
+        <v>62100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.43%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="H13" t="n">
         <v>41.76</v>
@@ -1622,7 +1622,7 @@
         <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>84374012000</v>
+        <v>86818165800</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,18 +1671,18 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7305</v>
+        <v>7320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>28</v>
@@ -1714,7 +1714,7 @@
         <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>9433758915</v>
+        <v>9748962445</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>223500</v>
+        <v>225000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G15" t="n">
-        <v>1350</v>
+        <v>1287</v>
       </c>
       <c r="H15" t="n">
         <v>46.17</v>
@@ -1806,7 +1806,7 @@
         <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>2539695424750</v>
+        <v>2686378520250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 논란 속 주가 하락 및 경영 퇴출 주장. 정책 및 시장 전반에 대한 부정적 인식.</t>
+          <t>이재용 상속세 관련 정치적 이슈와 삼성전자 주가 하락에 대한 부정적 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상속세', '주가 조작', '국장']</t>
+          <t>['상속세', '주가 하락', '정치']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,18 +1855,18 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54400</v>
+        <v>54300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-4.23%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F16" t="n">
         <v>219</v>
@@ -1898,7 +1898,7 @@
         <v>22.34</v>
       </c>
       <c r="O16" t="n">
-        <v>78887167300</v>
+        <v>82057361200</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11080</v>
+        <v>176100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.13</v>
+        <v>-0.13</v>
       </c>
       <c r="E17" t="n">
-        <v>397</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>1236</v>
+        <v>242</v>
       </c>
       <c r="H17" t="n">
-        <v>9.73</v>
+        <v>74.87</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,152 +1975,152 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>11620</v>
+        <v>183900</v>
       </c>
       <c r="K17" t="n">
-        <v>11300</v>
+        <v>176800</v>
       </c>
       <c r="L17" t="n">
-        <v>11470</v>
+        <v>179000</v>
       </c>
       <c r="M17" t="n">
-        <v>10890</v>
+        <v>168100</v>
       </c>
       <c r="N17" t="n">
-        <v>9.6</v>
+        <v>75</v>
       </c>
       <c r="O17" t="n">
-        <v>52394898000</v>
+        <v>600015911300</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>243500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>71000</v>
       </c>
       <c r="R17" t="n">
-        <v>-450000</v>
+        <v>-658000</v>
       </c>
       <c r="S17" t="n">
-        <v>-75000</v>
+        <v>-4000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>원전, 가덕도 공사비 증액, 공매도 금지 조치 등 정부 정책 관련 긍정적 기대감. 러시아-우크라이나 재건 사업 수혜 전망.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도 금지']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>175300</v>
+        <v>8180</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.68%</t>
+          <t>'-4.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="H18" t="n">
-        <v>74.87</v>
+        <v>2.67</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>183900</v>
+        <v>8580</v>
       </c>
       <c r="K18" t="n">
-        <v>176800</v>
+        <v>11090</v>
       </c>
       <c r="L18" t="n">
-        <v>179000</v>
+        <v>11150</v>
       </c>
       <c r="M18" t="n">
-        <v>168100</v>
+        <v>8070</v>
       </c>
       <c r="N18" t="n">
-        <v>75</v>
+        <v>2.66</v>
       </c>
       <c r="O18" t="n">
-        <v>580053715550</v>
+        <v>29550084590</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>19270</v>
       </c>
       <c r="Q18" t="n">
-        <v>71000</v>
+        <v>2135</v>
       </c>
       <c r="R18" t="n">
-        <v>-658000</v>
+        <v>-381000</v>
       </c>
       <c r="S18" t="n">
-        <v>-4000</v>
+        <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
+          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '증여세', '우선주 소각']</t>
+          <t>['영업이익', '환기', '광통신']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22450</v>
+        <v>22500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-4.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F19" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G19" t="n">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="H19" t="n">
         <v>11.6</v>
@@ -2174,7 +2174,7 @@
         <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>79823094125</v>
+        <v>82384394775</v>
       </c>
       <c r="P19" t="n">
         <v>59300</v>
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8150</v>
+        <v>11070</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-4.73%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>114</v>
+        <v>400</v>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="G20" t="n">
-        <v>294</v>
+        <v>1269</v>
       </c>
       <c r="H20" t="n">
-        <v>2.67</v>
+        <v>9.73</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8580</v>
+        <v>11620</v>
       </c>
       <c r="K20" t="n">
-        <v>11090</v>
+        <v>11300</v>
       </c>
       <c r="L20" t="n">
-        <v>11150</v>
+        <v>11470</v>
       </c>
       <c r="M20" t="n">
-        <v>8070</v>
+        <v>10890</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>9.6</v>
       </c>
       <c r="O20" t="n">
-        <v>29320608630</v>
+        <v>53696789575</v>
       </c>
       <c r="P20" t="n">
-        <v>19270</v>
+        <v>40350</v>
       </c>
       <c r="Q20" t="n">
-        <v>2135</v>
+        <v>3320</v>
       </c>
       <c r="R20" t="n">
-        <v>-381000</v>
+        <v>-450000</v>
       </c>
       <c r="S20" t="n">
-        <v>-1000</v>
+        <v>-75000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
+          <t>원전, 가덕도 공사비 증액, 공매도 금지 조치 등 정부 정책 관련 긍정적 기대감. 러시아-우크라이나 재건 사업 수혜 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['영업이익', '환기', '광통신']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6280</v>
+        <v>6320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.42%</t>
+          <t>'-4.82%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="n">
         <v>0.85</v>
@@ -2358,7 +2358,7 @@
         <v>0.9</v>
       </c>
       <c r="O21" t="n">
-        <v>31849877720</v>
+        <v>31997146770</v>
       </c>
       <c r="P21" t="n">
         <v>9820</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1431000</v>
+        <v>1440000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.23%</t>
+          <t>'-5.64%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G22" t="n">
-        <v>1296</v>
+        <v>1331</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3143960621000</v>
+        <v>3296630080500</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>엔비디아 회복 및 AI 투자 확대 기대감 속 개인 투자자들의 불안감 표출. 정부 정책 및 시장 하락에 대한 불만.</t>
+          <t>샌디스크 역대급 서프라이즈 및 AI 투자 확대 뉴스 기반의 단기 반등 기대감과 함께 정치적 비판이 혼재함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['엔비디아', 'AI 투자', '자사주 매수']</t>
+          <t>['AI 투자', '자사주 매입', '실적']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13880</v>
+        <v>13860</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.65%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G23" t="n">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>44477490655</v>
+        <v>45329532105</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>상승 기대감과 정부 정책에 대한 불신 혼재. 특허 및 루멘텀 관련 언급. 조정 시 매수 기회로 인식.</t>
+          <t>정부 정책 및 특허 기반의 광통신 섹터 수혜 기대감과 함께, 한국장 불신으로 인한 주가 하락에 대한 불만이 공존함.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '정부']</t>
+          <t>['광통신', '특허', '정책 수혜']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7170</v>
+        <v>7230</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-9.24%</t>
+          <t>'-8.48%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>16170976745</v>
+        <v>16303523560</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119300</v>
+        <v>119700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-13.68%</t>
+          <t>'-13.39%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F25" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G25" t="n">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>162372467600</v>
+        <v>169676083850</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대덕전자가 2시간 만에 13% 하락하며 투자자들의 불안감을 키우고 있습니다. 실적에 대한 기대와 달리 급락하는 이유에 대한 의문이 제기되고 있습니다.</t>
+          <t>실적 발표에도 불구하고 급락하는 주가에 대한 실망감과 기관 매도에 대한 불만이 표출됨.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '하락', '기판']</t>
+          <t>['실적', '급락', '기관 매도']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14100</v>
+        <v>14020</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-17.06%</t>
+          <t>'-17.53%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="F26" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>60639407995</v>
+        <v>61832021220</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 속 보호예수 물량 및 프로그램 매도 우려. 장비 수주 공시 및 ASML 관련 기대.</t>
+          <t>보호예수, 반도체 섹터 전반의 약세, 장난치는 듯한 주가 흐름에 대한 불만과 불안감이 나타남.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '장비 수주', '마이크론']</t>
+          <t>['보호예수', '반도체 약세', '주가 흐름']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1805</v>
+        <v>1900</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-29.90%</t>
+          <t>'-26.21%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G27" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>7489575672</v>
+        <v>7833596050</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>신규 상장 후 하한가 행진 및 상폐 우려. 납입 이슈와 주가 하락에 대한 불안감.</t>
+          <t>공모주 납입 연기 가능성 및 급격한 하락세에 대한 불안감과 함께 상폐 가능성에 대한 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상장', '하한가', '납입']</t>
+          <t>['공모주', '납입 연기', '상폐 우려']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10330</v>
+        <v>10280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-31.13%</t>
+          <t>'-31.47%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F28" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G28" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>130992610585</v>
+        <v>132446653605</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>인텔리빅스와의 실적 비교 우위 강조. 상장 초기 급등 기대감 및 주포 역할에 대한 관심.</t>
+          <t>높은 영업이익 대비 급락한 주가에 대한 실망감과 함께, 향후 상승에 대한 기대감을 보이는 의견이 존재함.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['당기순이익', '실적', '주포']</t>
+          <t>['영업이익', '주가 급락', '기대감']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_13.xlsx
+++ b/data/trending_integrated_20261030_13.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24300</v>
+        <v>24550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+170.00%</t>
+          <t>'+172.78%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,7 +581,7 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G2" t="n">
         <v>772</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>757712698890</v>
+        <v>773742616240</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 정책 지원 가능성과 AI 관련 성장 기대감을 보이는 한편, 급격한 가격 변동성에 대한 우려도 존재함.</t>
+          <t>인텔리빅스의 높은 상승률에 대한 기대감과 함께 정부의 AI 육성 정책 및 IPO 대장주로서의 전망 언급. 단기 급등락 패턴에 대한 주의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '신규상장', '주가 변동성']</t>
+          <t>['AI', 'IPO', '정부 정책']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19320</v>
+        <v>7530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.04%</t>
+          <t>'+20.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16650</v>
+        <v>6240</v>
       </c>
       <c r="K3" t="n">
-        <v>16830</v>
+        <v>6700</v>
       </c>
       <c r="L3" t="n">
-        <v>19900</v>
+        <v>7880</v>
       </c>
       <c r="M3" t="n">
-        <v>16750</v>
+        <v>6330</v>
       </c>
       <c r="N3" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>124838093280</v>
+        <v>32626017100</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>16620</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>4600</v>
       </c>
       <c r="R3" t="n">
-        <v>67000</v>
+        <v>-1000</v>
       </c>
       <c r="S3" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 양자 보안 의무화 및 해킹 사태 수혜주로서 단기 급등에 대한 기대감이 높으며, 기술력에 대한 긍정적 평가가 있음.</t>
+          <t>지수 급락 속 상한가 기대감. 건설업 활성화와 주포의 움직임 관찰. 유증 성공 여부 주목.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자 보안', '해킹 수혜', '기술력']</t>
+          <t>['상한가', '건설', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7180</v>
+        <v>19370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.06%</t>
+          <t>'+16.34%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6240</v>
+        <v>16650</v>
       </c>
       <c r="K4" t="n">
-        <v>6700</v>
+        <v>16830</v>
       </c>
       <c r="L4" t="n">
-        <v>7880</v>
+        <v>19900</v>
       </c>
       <c r="M4" t="n">
-        <v>6330</v>
+        <v>16750</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>31413870875</v>
+        <v>126443058185</v>
       </c>
       <c r="P4" t="n">
-        <v>16620</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>4600</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-1000</v>
+        <v>67000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>지수 급락 속 상한가 기대감. 건설업 활성화와 주포의 움직임 관찰. 유증 성공 여부 주목.</t>
+          <t>정부의 양자 보안 의무화 정책 및 바이낸스/빗썸 해킹 사태로 인한 라온시큐어의 최대 수혜주로서의 기대감 상승. 기술력 및 보안 대장주로서의 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['상한가', '건설', '주포']</t>
+          <t>['양자 보안', '해킹', '수혜주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2775</v>
+        <v>8770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.27%</t>
+          <t>'+13.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.79</v>
+        <v>13.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2450</v>
+        <v>7700</v>
       </c>
       <c r="K5" t="n">
-        <v>2460</v>
+        <v>9360</v>
       </c>
       <c r="L5" t="n">
-        <v>3110</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>2335</v>
+        <v>8430</v>
       </c>
       <c r="N5" t="n">
-        <v>0.63</v>
+        <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>12682189998</v>
+        <v>8967148140</v>
       </c>
       <c r="P5" t="n">
-        <v>3170</v>
+        <v>13670</v>
       </c>
       <c r="Q5" t="n">
-        <v>880</v>
+        <v>7060</v>
       </c>
       <c r="R5" t="n">
-        <v>-23000</v>
+        <v>-70000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['임상 3상', '위식도염', '시장 규모']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8680</v>
+        <v>2785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.73%</t>
+          <t>'+13.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>13.29</v>
+        <v>0.79</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7700</v>
+        <v>2450</v>
       </c>
       <c r="K6" t="n">
-        <v>9360</v>
+        <v>2460</v>
       </c>
       <c r="L6" t="n">
-        <v>9500</v>
+        <v>3110</v>
       </c>
       <c r="M6" t="n">
-        <v>8430</v>
+        <v>2335</v>
       </c>
       <c r="N6" t="n">
-        <v>12.92</v>
+        <v>0.63</v>
       </c>
       <c r="O6" t="n">
-        <v>8613549080</v>
+        <v>12696463848</v>
       </c>
       <c r="P6" t="n">
-        <v>13670</v>
+        <v>3170</v>
       </c>
       <c r="Q6" t="n">
-        <v>7060</v>
+        <v>880</v>
       </c>
       <c r="R6" t="n">
-        <v>-70000</v>
+        <v>-23000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상 3상', '위식도염', '시장 규모']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51600</v>
+        <v>11940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.09%</t>
+          <t>'+6.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.82</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="G7" t="n">
-        <v>236</v>
+        <v>919</v>
       </c>
       <c r="H7" t="n">
-        <v>23.82</v>
+        <v>15.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49100</v>
+        <v>11200</v>
       </c>
       <c r="K7" t="n">
-        <v>49450</v>
+        <v>13500</v>
       </c>
       <c r="L7" t="n">
-        <v>52000</v>
+        <v>13710</v>
       </c>
       <c r="M7" t="n">
-        <v>48050</v>
+        <v>11620</v>
       </c>
       <c r="N7" t="n">
-        <v>24.64</v>
+        <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>62192078100</v>
+        <v>55480272945</v>
       </c>
       <c r="P7" t="n">
-        <v>97900</v>
+        <v>18960</v>
       </c>
       <c r="Q7" t="n">
-        <v>30950</v>
+        <v>5730</v>
       </c>
       <c r="R7" t="n">
-        <v>2000</v>
+        <v>-396000</v>
       </c>
       <c r="S7" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>역대 최대 실적 발표에도 불구하고 주가가 지지부진한 상황에 대한 불만과 함께, 공매도 세력과의 공방 속 상승 기대감이 있음.</t>
+          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적', '공매도', 'TC본더']</t>
+          <t>['LED', '기술개발', '시장석권']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29450</v>
+        <v>15650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.99%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>323</v>
+        <v>406</v>
       </c>
       <c r="H8" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,143 +1147,143 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K8" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L8" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M8" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>121672983950</v>
+        <v>52730398245</v>
       </c>
       <c r="P8" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>-12000</v>
+        <v>101000</v>
       </c>
       <c r="S8" t="n">
-        <v>188000</v>
+        <v>189000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 미국 보험 등재 기대. 공매도 영향 속 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['FDA 승인', '공매도', '헬스케어']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15680</v>
+        <v>51200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.67%</t>
+          <t>'+4.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>394</v>
+        <v>242</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>51620635620</v>
+        <v>63141828500</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R9" t="n">
-        <v>101000</v>
+        <v>2000</v>
       </c>
       <c r="S9" t="n">
-        <v>189000</v>
+        <v>69000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 미국 보험 등재 기대. 공매도 영향 속 상승 추세 전망.</t>
+          <t>역대 최대 실적 발표에도 불구하고 주가가 지지부진한 상황에 대한 불만과 함께, 공매도 세력과의 공방 속 상승 기대감이 있음.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '헬스케어']</t>
+          <t>['실적', '공매도', 'TC본더']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11710</v>
+        <v>29250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.55%</t>
+          <t>'+4.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.04</v>
+        <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>915</v>
+        <v>332</v>
       </c>
       <c r="H10" t="n">
-        <v>15.04</v>
+        <v>4.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11200</v>
+        <v>28050</v>
       </c>
       <c r="K10" t="n">
-        <v>13500</v>
+        <v>27850</v>
       </c>
       <c r="L10" t="n">
-        <v>13710</v>
+        <v>30400</v>
       </c>
       <c r="M10" t="n">
-        <v>11620</v>
+        <v>27650</v>
       </c>
       <c r="N10" t="n">
-        <v>15.08</v>
+        <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>54564939160</v>
+        <v>123003431900</v>
       </c>
       <c r="P10" t="n">
-        <v>18960</v>
+        <v>50600</v>
       </c>
       <c r="Q10" t="n">
-        <v>5730</v>
+        <v>13210</v>
       </c>
       <c r="R10" t="n">
-        <v>-396000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>188000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['LED', '기술개발', '시장석권']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15820</v>
+        <v>15770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
         <v>326</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>48120663680</v>
+        <v>49373288270</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4055</v>
+        <v>4045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>79966009615</v>
+        <v>80576209648</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62100</v>
+        <v>62000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.11%</t>
+          <t>'-1.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
         <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H13" t="n">
         <v>41.76</v>
@@ -1622,7 +1622,7 @@
         <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>86818165800</v>
+        <v>90670023950</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7320</v>
+        <v>7300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="H14" t="n">
         <v>25.3</v>
@@ -1714,7 +1714,7 @@
         <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>9748962445</v>
+        <v>10132050395</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>225000</v>
+        <v>8390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>522</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>1287</v>
+        <v>304</v>
       </c>
       <c r="H15" t="n">
-        <v>46.17</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>232000</v>
+        <v>8580</v>
       </c>
       <c r="K15" t="n">
-        <v>223500</v>
+        <v>11090</v>
       </c>
       <c r="L15" t="n">
-        <v>229500</v>
+        <v>11150</v>
       </c>
       <c r="M15" t="n">
-        <v>216500</v>
+        <v>8070</v>
       </c>
       <c r="N15" t="n">
-        <v>46.19</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>2686378520250</v>
+        <v>29725031695</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>19270</v>
       </c>
       <c r="Q15" t="n">
-        <v>94500</v>
+        <v>2135</v>
       </c>
       <c r="R15" t="n">
-        <v>664000</v>
+        <v>-381000</v>
       </c>
       <c r="S15" t="n">
-        <v>-505000</v>
+        <v>-1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 상속세 관련 정치적 이슈와 삼성전자 주가 하락에 대한 부정적 언급이 주를 이룸.</t>
+          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상속세', '주가 하락', '정치']</t>
+          <t>['영업이익', '환기', '광통신']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54300</v>
+        <v>226000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.23%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>328</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>219</v>
+        <v>525</v>
       </c>
       <c r="G16" t="n">
-        <v>1070</v>
+        <v>1254</v>
       </c>
       <c r="H16" t="n">
-        <v>22.14</v>
+        <v>46.17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>56700</v>
+        <v>232000</v>
       </c>
       <c r="K16" t="n">
-        <v>55500</v>
+        <v>223500</v>
       </c>
       <c r="L16" t="n">
-        <v>55900</v>
+        <v>229500</v>
       </c>
       <c r="M16" t="n">
-        <v>53700</v>
+        <v>216500</v>
       </c>
       <c r="N16" t="n">
-        <v>22.34</v>
+        <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>82057361200</v>
+        <v>2787078505500</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>53400</v>
+        <v>94500</v>
       </c>
       <c r="R16" t="n">
-        <v>-238000</v>
+        <v>664000</v>
       </c>
       <c r="S16" t="n">
-        <v>-81000</v>
+        <v>-505000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
+          <t>이재용 상속세 및 정부 정책 관련 비판과 함께 삼성전자 주가 하락에 대한 불만 표출. 일부에서는 주가 조작 및 경영 손떼기 주장.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['상속세', '주가 조작', '경영']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>176100</v>
+        <v>176900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.24%</t>
+          <t>'-3.81%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.13</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="H17" t="n">
         <v>74.87</v>
@@ -1990,7 +1990,7 @@
         <v>75</v>
       </c>
       <c r="O17" t="n">
-        <v>600015911300</v>
+        <v>614609459400</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8180</v>
+        <v>6380</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.66%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="H18" t="n">
-        <v>2.67</v>
+        <v>0.85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8580</v>
+        <v>6640</v>
       </c>
       <c r="K18" t="n">
-        <v>11090</v>
+        <v>7210</v>
       </c>
       <c r="L18" t="n">
-        <v>11150</v>
+        <v>7500</v>
       </c>
       <c r="M18" t="n">
-        <v>8070</v>
+        <v>6230</v>
       </c>
       <c r="N18" t="n">
-        <v>2.66</v>
+        <v>0.9</v>
       </c>
       <c r="O18" t="n">
-        <v>29550084590</v>
+        <v>32052035300</v>
       </c>
       <c r="P18" t="n">
-        <v>19270</v>
+        <v>9820</v>
       </c>
       <c r="Q18" t="n">
-        <v>2135</v>
+        <v>4000</v>
       </c>
       <c r="R18" t="n">
-        <v>-381000</v>
+        <v>-55000</v>
       </c>
       <c r="S18" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['영업이익', '환기', '광통신']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22500</v>
+        <v>22650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.66%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F19" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G19" t="n">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="H19" t="n">
         <v>11.6</v>
@@ -2174,7 +2174,7 @@
         <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>82384394775</v>
+        <v>84353462150</v>
       </c>
       <c r="P19" t="n">
         <v>59300</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11070</v>
+        <v>54100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.73%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="E20" t="n">
-        <v>400</v>
+        <v>336</v>
       </c>
       <c r="F20" t="n">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="G20" t="n">
-        <v>1269</v>
+        <v>1073</v>
       </c>
       <c r="H20" t="n">
-        <v>9.73</v>
+        <v>22.14</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11620</v>
+        <v>56700</v>
       </c>
       <c r="K20" t="n">
-        <v>11300</v>
+        <v>55500</v>
       </c>
       <c r="L20" t="n">
-        <v>11470</v>
+        <v>55900</v>
       </c>
       <c r="M20" t="n">
-        <v>10890</v>
+        <v>53700</v>
       </c>
       <c r="N20" t="n">
-        <v>9.6</v>
+        <v>22.34</v>
       </c>
       <c r="O20" t="n">
-        <v>53696789575</v>
+        <v>83140438550</v>
       </c>
       <c r="P20" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>3320</v>
+        <v>53400</v>
       </c>
       <c r="R20" t="n">
-        <v>-450000</v>
+        <v>-238000</v>
       </c>
       <c r="S20" t="n">
-        <v>-75000</v>
+        <v>-81000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>원전, 가덕도 공사비 증액, 공매도 금지 조치 등 정부 정책 관련 긍정적 기대감. 러시아-우크라이나 재건 사업 수혜 전망.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 관련 긍정적 언급. 다만, 정부 정책 및 시장 상황에 대한 부정적 평가가 sentiment에 영향을 미치며 fact score는 구체적인 수주 내용을 기반으로 산정.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도 금지']</t>
+          <t>['SMR', '원자로 수주', '실적']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,99 +2304,99 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6320</v>
+        <v>11040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.82%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>407</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="G21" t="n">
-        <v>82</v>
+        <v>1307</v>
       </c>
       <c r="H21" t="n">
-        <v>0.85</v>
+        <v>9.73</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6640</v>
+        <v>11620</v>
       </c>
       <c r="K21" t="n">
-        <v>7210</v>
+        <v>11300</v>
       </c>
       <c r="L21" t="n">
-        <v>7500</v>
+        <v>11470</v>
       </c>
       <c r="M21" t="n">
-        <v>6230</v>
+        <v>10890</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>31997146770</v>
+        <v>54430606345</v>
       </c>
       <c r="P21" t="n">
-        <v>9820</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>4000</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-55000</v>
+        <v>-450000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-75000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>정부 정책(원전, 가덕도 증액, 공매도 금지) 및 한수원 관련 이슈에 대한 긍정적 해석. 재건 사업 전망 및 공매도 금지 조치로 인한 기대감.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1440000</v>
+        <v>1442000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.64%</t>
+          <t>'-5.50%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="G22" t="n">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3296630080500</v>
+        <v>3389022047500</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>샌디스크 역대급 서프라이즈 및 AI 투자 확대 뉴스 기반의 단기 반등 기대감과 함께 정치적 비판이 혼재함.</t>
+          <t>SK하이닉스 주가 상승 기대감과 함께 정부 정책 및 정치권에 대한 비판적인 내용 혼재. 자사주 매입 및 AI 투자 확대 뉴스 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['AI 투자', '자사주 매입', '실적']</t>
+          <t>['AI 투자', '자사주 매입', '정치권 비판']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13860</v>
+        <v>13920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F23" t="n">
         <v>68</v>
       </c>
       <c r="G23" t="n">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>45329532105</v>
+        <v>45909199095</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>정부 정책 및 특허 기반의 광통신 섹터 수혜 기대감과 함께, 한국장 불신으로 인한 주가 하락에 대한 불만이 공존함.</t>
+          <t>미국 광통신주 강세 및 특허 보유 사실을 근거로 대한광통신의 주가 상승에 대한 기대감 표출. 정부 정책 불신 속에서도 긍정적 전망 유지.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '정책 수혜']</t>
+          <t>['광통신', '특허', '주가 상승']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7230</v>
+        <v>7190</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-8.48%</t>
+          <t>'-8.99%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
         <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>16303523560</v>
+        <v>16533227735</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119700</v>
+        <v>119400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-13.39%</t>
+          <t>'-13.60%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F25" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G25" t="n">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>169676083850</v>
+        <v>174739594000</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 발표에도 불구하고 급락하는 주가에 대한 실망감과 기관 매도에 대한 불만이 표출됨.</t>
+          <t>실적 발표 후 급락한 대덕전자에 대한 실망감과 의문 제기. 기관 매수 부진 및 타 증권사 목표가 상향에도 불구하고 하락세 지속.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', '급락', '기관 매도']</t>
+          <t>['실적 발표', '급락', '기관 매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14020</v>
+        <v>14290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-17.53%</t>
+          <t>'-15.94%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G26" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>61832021220</v>
+        <v>63603049525</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수, 반도체 섹터 전반의 약세, 장난치는 듯한 주가 흐름에 대한 불만과 불안감이 나타남.</t>
+          <t>멜콘의 급락 및 보호예수 관련 우려 속에 주가 반등에 대한 기대감과 실망감이 혼재. 반도체 업황 부진 및 장세 불안정성 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체 약세', '주가 흐름']</t>
+          <t>['보호예수', '급락', '반도체']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1900</v>
+        <v>1847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-26.21%</t>
+          <t>'-28.27%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F27" t="n">
         <v>54</v>
       </c>
       <c r="G27" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>7833596050</v>
+        <v>8038094642</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>공모주 납입 연기 가능성 및 급격한 하락세에 대한 불안감과 함께 상폐 가능성에 대한 우려가 제기됨.</t>
+          <t>벡트로보틱스의 연이은 하한가 및 상폐 가능성에 대한 우려. 납입 공시 지연 및 주가 하락에 대한 불안감.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['공모주', '납입 연기', '상폐 우려']</t>
+          <t>['하한가', '상폐', '납입 공시']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10280</v>
+        <v>10270</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-31.47%</t>
+          <t>'-31.53%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="F28" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G28" t="n">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>132446653605</v>
+        <v>133012124090</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>높은 영업이익 대비 급락한 주가에 대한 실망감과 함께, 향후 상승에 대한 기대감을 보이는 의견이 존재함.</t>
+          <t>크리에이츠의 상장 직후 급락에 대한 실망감과 함께 높은 영업이익 대비 주가 부진에 대한 의문. 인텔리빅스와의 실적 비교 언급.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 급락', '기대감']</t>
+          <t>['상장', '영업이익', '주가 부진']</t>
         </is>
       </c>
       <c r="X28" t="n">

--- a/data/trending_integrated_20261030_13.xlsx
+++ b/data/trending_integrated_20261030_13.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24550</v>
+        <v>23250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+172.78%</t>
+          <t>'+158.33%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G2" t="n">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>773742616240</v>
+        <v>786854783165</v>
       </c>
       <c r="P2" t="n">
         <v>27100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인텔리빅스의 높은 상승률에 대한 기대감과 함께 정부의 AI 육성 정책 및 IPO 대장주로서의 전망 언급. 단기 급등락 패턴에 대한 주의.</t>
+          <t>인텔리빅스의 급등세 지속. AI 관련주로 정부 지원 기대감. 신규 상장주로서 높은 변동성 및 단기 급등 패턴 관찰. 3파동 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '정부 정책']</t>
+          <t>['AI', '신규 상장주', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7530</v>
+        <v>7730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.67%</t>
+          <t>'+23.88%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>6700</v>
       </c>
       <c r="L3" t="n">
-        <v>7880</v>
+        <v>7980</v>
       </c>
       <c r="M3" t="n">
         <v>6330</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>32626017100</v>
+        <v>35521415025</v>
       </c>
       <c r="P3" t="n">
         <v>16620</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>지수 급락 속 상한가 기대감. 건설업 활성화와 주포의 움직임 관찰. 유증 성공 여부 주목.</t>
+          <t>상지건설의 주가 상승 및 하락 반복. 유증 성공 기대감과 함께 주가 부양 의지 표출. 건설 산업 회복 및 재료 부각 필요성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상한가', '건설', '주포']</t>
+          <t>['유상증자', '주가 부양', '건설주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19370</v>
+        <v>19530</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.34%</t>
+          <t>'+17.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>126443058185</v>
+        <v>127612556130</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8770</v>
+        <v>8760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.90%</t>
+          <t>'+13.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>8967148140</v>
+        <v>9054339560</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -978,7 +978,7 @@
         <v>0.63</v>
       </c>
       <c r="O6" t="n">
-        <v>12696463848</v>
+        <v>12726243593</v>
       </c>
       <c r="P6" t="n">
         <v>3170</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11940</v>
+        <v>12180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.61%</t>
+          <t>'+8.75%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F7" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="G7" t="n">
-        <v>919</v>
+        <v>946</v>
       </c>
       <c r="H7" t="n">
         <v>15.04</v>
@@ -1070,7 +1070,7 @@
         <v>15.08</v>
       </c>
       <c r="O7" t="n">
-        <v>55480272945</v>
+        <v>57389865030</v>
       </c>
       <c r="P7" t="n">
         <v>18960</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색LED 개발 성공 및 100억달러 시장 석권 전망. 하락장 속 견조한 흐름과 외국인, 기관 매수세 관찰.</t>
+          <t>서울반도체의 혁신 기술 개발 및 시장 석권 기대감. 희토류 없는 백색 LED 개발 성공. 공매도 폐지 요구 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['LED', '기술개발', '시장석권']</t>
+          <t>['백색 LED', '희토류', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15650</v>
+        <v>15690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.47%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H8" t="n">
         <v>7.15</v>
@@ -1162,7 +1162,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>52730398245</v>
+        <v>53546519625</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 미국 보험 등재 기대. 공매도 영향 속 상승 추세 전망.</t>
+          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '헬스케어']</t>
+          <t>['FDA 승인', '유방암', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51200</v>
+        <v>51400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.28%</t>
+          <t>'+4.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
         <v>242</v>
@@ -1254,7 +1254,7 @@
         <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>63141828500</v>
+        <v>64119926400</v>
       </c>
       <c r="P9" t="n">
         <v>97900</v>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29250</v>
+        <v>29300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.28%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
         <v>48</v>
@@ -1346,7 +1346,7 @@
         <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>123003431900</v>
+        <v>123766112650</v>
       </c>
       <c r="P10" t="n">
         <v>50600</v>
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15770</v>
+        <v>4050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>326</v>
+        <v>207</v>
       </c>
       <c r="H11" t="n">
-        <v>28.13</v>
+        <v>1.43</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15720</v>
+        <v>4040</v>
       </c>
       <c r="K11" t="n">
-        <v>15420</v>
+        <v>3925</v>
       </c>
       <c r="L11" t="n">
-        <v>16050</v>
+        <v>4265</v>
       </c>
       <c r="M11" t="n">
-        <v>15320</v>
+        <v>3880</v>
       </c>
       <c r="N11" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>49373288270</v>
+        <v>81115332418</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>15320</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>700000</v>
+        <v>78000</v>
       </c>
       <c r="S11" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 조선주 약세 속 미국 조선주 HII 폭등 비교. 3분기 실적 서프라이즈 기대와 정기선 승계 및 증여세와의 상관관계 의문 제기.</t>
+          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '승계']</t>
+          <t>['상승', '기대감', '외국인매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4045</v>
+        <v>15740</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.13%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.77</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>206</v>
+        <v>336</v>
       </c>
       <c r="H12" t="n">
-        <v>1.43</v>
+        <v>28.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4040</v>
+        <v>15720</v>
       </c>
       <c r="K12" t="n">
-        <v>3925</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>4265</v>
+        <v>16050</v>
       </c>
       <c r="M12" t="n">
-        <v>3880</v>
+        <v>15320</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>80576209648</v>
+        <v>50729233670</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>15320</v>
       </c>
       <c r="R12" t="n">
-        <v>78000</v>
+        <v>700000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 시장 폭락 속에서도 견조한 흐름 보이는 빛과전자. 50층 돌파 및 6천원 도달 기대감. 외국인, 프로그램 매수세 관찰.</t>
+          <t>국내 조선주 약세 속 미국 조선주 HII 폭등 비교. 3분기 실적 서프라이즈 기대와 정기선 승계 및 증여세와의 상관관계 의문 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['상승', '기대감', '외국인매수']</t>
+          <t>['조선주', '실적', '승계']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,99 +1568,99 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62000</v>
+        <v>8500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.27%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="H13" t="n">
-        <v>41.76</v>
+        <v>2.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62800</v>
+        <v>8580</v>
       </c>
       <c r="K13" t="n">
-        <v>62300</v>
+        <v>11090</v>
       </c>
       <c r="L13" t="n">
-        <v>62800</v>
+        <v>11150</v>
       </c>
       <c r="M13" t="n">
-        <v>60700</v>
+        <v>8070</v>
       </c>
       <c r="N13" t="n">
-        <v>41.55</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>90670023950</v>
+        <v>29909883095</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>19270</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>2135</v>
       </c>
       <c r="R13" t="n">
-        <v>55000</v>
+        <v>-381000</v>
       </c>
       <c r="S13" t="n">
-        <v>-81000</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
         <v>25.3</v>
@@ -1714,7 +1714,7 @@
         <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>10132050395</v>
+        <v>10273796860</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1759,92 +1759,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8390</v>
+        <v>61500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="H15" t="n">
-        <v>2.67</v>
+        <v>41.76</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8580</v>
+        <v>62800</v>
       </c>
       <c r="K15" t="n">
-        <v>11090</v>
+        <v>62300</v>
       </c>
       <c r="L15" t="n">
-        <v>11150</v>
+        <v>62800</v>
       </c>
       <c r="M15" t="n">
-        <v>8070</v>
+        <v>60700</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>41.55</v>
       </c>
       <c r="O15" t="n">
-        <v>29725031695</v>
+        <v>93254479200</v>
       </c>
       <c r="P15" t="n">
-        <v>19270</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>2135</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>-381000</v>
+        <v>55000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>-81000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>서울바이오시스가 서울반도체보다 높은 영업이익을 기록하며 역전을 기대하고 있습니다. 내년 3월 환기 해제 예정이며, 독점 기술력과 광통신 사업 가세로 매출 조단위 달성 전망이 있습니다.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업이익', '환기', '광통신']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>226000</v>
+        <v>226250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="G16" t="n">
-        <v>1254</v>
+        <v>1286</v>
       </c>
       <c r="H16" t="n">
         <v>46.17</v>
@@ -1898,7 +1898,7 @@
         <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>2787078505500</v>
+        <v>2886921856500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 상속세 및 정부 정책 관련 비판과 함께 삼성전자 주가 하락에 대한 불만 표출. 일부에서는 주가 조작 및 경영 손떼기 주장.</t>
+          <t>삼성전자 주가 하락에 대한 정치적 불만 표출. 이재용 경영 퇴진 요구. 재료 소멸 및 주가 부양 의지 부재 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상속세', '주가 조작', '경영']</t>
+          <t>['상속세', '이재용', '주가 부양']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.13</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H17" t="n">
         <v>74.87</v>
@@ -1990,7 +1990,7 @@
         <v>75</v>
       </c>
       <c r="O17" t="n">
-        <v>614609459400</v>
+        <v>632244538750</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2035,184 +2035,184 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6380</v>
+        <v>22600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>265</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="G18" t="n">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="H18" t="n">
-        <v>0.85</v>
+        <v>11.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6640</v>
+        <v>23600</v>
       </c>
       <c r="K18" t="n">
-        <v>7210</v>
+        <v>22650</v>
       </c>
       <c r="L18" t="n">
-        <v>7500</v>
+        <v>22750</v>
       </c>
       <c r="M18" t="n">
-        <v>6230</v>
+        <v>21100</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9</v>
+        <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>32052035300</v>
+        <v>86538507450</v>
       </c>
       <c r="P18" t="n">
-        <v>9820</v>
+        <v>59300</v>
       </c>
       <c r="Q18" t="n">
-        <v>4000</v>
+        <v>21100</v>
       </c>
       <c r="R18" t="n">
-        <v>-55000</v>
+        <v>-650000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-235000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>한화솔루션의 주가 급락에 대한 의혹 제기. RE100 승인 및 카터스빌 물량 완판 소식에도 불구하고 주가 부진. 실적 턴어라운드에도 불구하고 주가 하락.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['주가 누르기', 'RE100', '실적 턴어라운드']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22650</v>
+        <v>6350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-4.37%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.63</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>261</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>174</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="H19" t="n">
-        <v>11.6</v>
+        <v>0.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23600</v>
+        <v>6640</v>
       </c>
       <c r="K19" t="n">
-        <v>22650</v>
+        <v>7210</v>
       </c>
       <c r="L19" t="n">
-        <v>22700</v>
+        <v>7500</v>
       </c>
       <c r="M19" t="n">
-        <v>21100</v>
+        <v>6230</v>
       </c>
       <c r="N19" t="n">
-        <v>12.23</v>
+        <v>0.9</v>
       </c>
       <c r="O19" t="n">
-        <v>84353462150</v>
+        <v>32107497740</v>
       </c>
       <c r="P19" t="n">
-        <v>59300</v>
+        <v>9820</v>
       </c>
       <c r="Q19" t="n">
-        <v>21100</v>
+        <v>4000</v>
       </c>
       <c r="R19" t="n">
-        <v>-650000</v>
+        <v>-55000</v>
       </c>
       <c r="S19" t="n">
-        <v>-235000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 누르기 의혹, 유증 및 실적 턴어라운드에도 불구하고 지속되는 급락에 대한 불만. 긍정적 실적 지표 언급에도 불구하고 주가 하락에 대한 부정적 심리가 강함.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 누르기', '유증', '실적']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54100</v>
+        <v>54000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.76%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.2</v>
       </c>
       <c r="E20" t="n">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F20" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G20" t="n">
-        <v>1073</v>
+        <v>1109</v>
       </c>
       <c r="H20" t="n">
         <v>22.14</v>
@@ -2266,7 +2266,7 @@
         <v>22.34</v>
       </c>
       <c r="O20" t="n">
-        <v>83140438550</v>
+        <v>84995695400</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11040</v>
+        <v>1444000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E21" t="n">
-        <v>407</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>181</v>
+        <v>507</v>
       </c>
       <c r="G21" t="n">
-        <v>1307</v>
+        <v>1274</v>
       </c>
       <c r="H21" t="n">
-        <v>9.73</v>
+        <v>48.72</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,47 +2343,47 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>11620</v>
+        <v>1526000</v>
       </c>
       <c r="K21" t="n">
-        <v>11300</v>
+        <v>1444000</v>
       </c>
       <c r="L21" t="n">
-        <v>11470</v>
+        <v>1449000</v>
       </c>
       <c r="M21" t="n">
-        <v>10890</v>
+        <v>1381000</v>
       </c>
       <c r="N21" t="n">
-        <v>9.6</v>
+        <v>48.66</v>
       </c>
       <c r="O21" t="n">
-        <v>54430606345</v>
+        <v>3503167268500</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>501000</v>
       </c>
       <c r="R21" t="n">
-        <v>-450000</v>
+        <v>-202000</v>
       </c>
       <c r="S21" t="n">
-        <v>-75000</v>
+        <v>-107000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>정부 정책(원전, 가덕도 증액, 공매도 금지) 및 한수원 관련 이슈에 대한 긍정적 해석. 재건 사업 전망 및 공매도 금지 조치로 인한 기대감.</t>
+          <t>SK하이닉스 주가 반등 기대와 자사주 매입 언급. AI 투자 확대 뉴스 및 실적 개선 전망. 정치적 이슈와 연기금 관련 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도 금지']</t>
+          <t>['자사주 매입', 'AI 투자', '실적 전망']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1442000</v>
+        <v>10990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.50%</t>
+          <t>'-5.42%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>414</v>
       </c>
       <c r="F22" t="n">
-        <v>508</v>
+        <v>182</v>
       </c>
       <c r="G22" t="n">
-        <v>1338</v>
+        <v>1323</v>
       </c>
       <c r="H22" t="n">
-        <v>48.72</v>
+        <v>9.73</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,47 +2435,47 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1526000</v>
+        <v>11620</v>
       </c>
       <c r="K22" t="n">
-        <v>1444000</v>
+        <v>11300</v>
       </c>
       <c r="L22" t="n">
-        <v>1446000</v>
+        <v>11470</v>
       </c>
       <c r="M22" t="n">
-        <v>1381000</v>
+        <v>10890</v>
       </c>
       <c r="N22" t="n">
-        <v>48.66</v>
+        <v>9.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3389022047500</v>
+        <v>55451145125</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q22" t="n">
-        <v>501000</v>
+        <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-202000</v>
+        <v>-450000</v>
       </c>
       <c r="S22" t="n">
-        <v>-107000</v>
+        <v>-75000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 상승 기대감과 함께 정부 정책 및 정치권에 대한 비판적인 내용 혼재. 자사주 매입 및 AI 투자 확대 뉴스 언급.</t>
+          <t>정부 정책(원전, 가덕도 증액, 공매도 금지) 및 한수원 관련 이슈에 대한 긍정적 해석. 재건 사업 전망 및 공매도 금지 조치로 인한 기대감.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['AI 투자', '자사주 매입', '정치권 비판']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13920</v>
+        <v>13980</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.39%</t>
+          <t>'-6.99%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F23" t="n">
         <v>68</v>
       </c>
       <c r="G23" t="n">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>45909199095</v>
+        <v>46502766380</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7190</v>
+        <v>7180</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-8.99%</t>
+          <t>'-9.11%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>16533227735</v>
+        <v>16621330950</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119400</v>
+        <v>120100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-13.60%</t>
+          <t>'-13.10%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F25" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G25" t="n">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>174739594000</v>
+        <v>180323011100</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 발표 후 급락한 대덕전자에 대한 실망감과 의문 제기. 기관 매수 부진 및 타 증권사 목표가 상향에도 불구하고 하락세 지속.</t>
+          <t>대덕전자의 급락세에 대한 실망감 표출. 실적 호조에도 불구하고 주가 하락 지속. 기관 매수세 부재 및 개인 투자자 손실 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적 발표', '급락', '기관 매수']</t>
+          <t>['실적', '주가 급락', '기관 매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14290</v>
+        <v>14260</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-15.94%</t>
+          <t>'-16.12%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F26" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G26" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>63603049525</v>
+        <v>65515713365</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>멜콘의 급락 및 보호예수 관련 우려 속에 주가 반등에 대한 기대감과 실망감이 혼재. 반도체 업황 부진 및 장세 불안정성 언급.</t>
+          <t>멜콘의 급락 및 변동성에 대한 불만 표출. 보호예수 및 시장 상황 악화 영향. 반도체 업황 부진 및 프로그램 매도 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '반도체']</t>
+          <t>['보호예수', '반도체', '급락']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1847</v>
+        <v>1838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-28.27%</t>
+          <t>'-28.62%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8038094642</v>
+        <v>8119687158</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>벡트로보틱스의 연이은 하한가 및 상폐 가능성에 대한 우려. 납입 공시 지연 및 주가 하락에 대한 불안감.</t>
+          <t>벡트로보틱스의 하한가 행진에 대한 우려. 납입 관련 이슈 및 상장폐지 가능성 제기. 대규모 하락 및 개인 투자자 손실 예상.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['하한가', '상폐', '납입 공시']</t>
+          <t>['하한가', '납입', '상장폐지']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10270</v>
+        <v>10280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-31.53%</t>
+          <t>'-31.47%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="F28" t="n">
         <v>223</v>
       </c>
       <c r="G28" t="n">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>133012124090</v>
+        <v>135001660015</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>
